--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF24AC85-B7D9-46BF-B66F-3EDDE84C487C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XuatKho_BH" sheetId="10" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_BH!$A$1:$M$22</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -116,8 +129,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;\ _₫_-;_-@_-"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -388,7 +401,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -406,7 +419,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -427,7 +440,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -442,7 +455,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -454,6 +467,63 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -483,63 +553,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -964,66 +977,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="45" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="47"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="48" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="50" t="s">
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="51"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="41"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="25"/>
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
@@ -1120,13 +1133,13 @@
       <c r="H12" s="20"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
       <c r="F13" s="22">
         <f>SUM(F12:F12)</f>
         <v>0</v>
@@ -1145,40 +1158,40 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8" s="2" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="25" t="s">
+      <c r="B15" s="47"/>
+      <c r="C15" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="25"/>
-      <c r="G15" s="27" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="H15" s="27"/>
+      <c r="H15" s="46"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="48"/>
+      <c r="C16" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="31" t="s">
+      <c r="D16" s="49"/>
+      <c r="E16" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32" t="s">
+      <c r="F16" s="50"/>
+      <c r="G16" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
@@ -1231,22 +1244,22 @@
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25" t="s">
+      <c r="B22" s="43"/>
+      <c r="C22" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26" t="s">
+      <c r="D22" s="44"/>
+      <c r="E22" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="26"/>
-      <c r="G22" s="27" t="s">
+      <c r="F22" s="45"/>
+      <c r="G22" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="46"/>
     </row>
     <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1272,12 +1285,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:H1"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C22:D22"/>
@@ -1291,6 +1298,12 @@
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
